--- a/3. MusicAndArts/1. CarnaticMusicPlusOthers/0. Books/SahajayogaBhajansAndNotes/0. Bhajans_WithWordToWordTranslations/4.4. HW-19012026-Music_Raga-Bilawal_Jaaga-Uthe_Song_Breakdown.xlsx
+++ b/3. MusicAndArts/1. CarnaticMusicPlusOthers/0. Books/SahajayogaBhajansAndNotes/0. Bhajans_WithWordToWordTranslations/4.4. HW-19012026-Music_Raga-Bilawal_Jaaga-Uthe_Song_Breakdown.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GoogleDriveSync\VirataHomeSchool\2. ClassMaterial\3. MusicAndArts\1. CarnaticMusicPlusOthers\0. Books\SahajayogaBhajansAndNotes\0. Bhajans_WithWordToWordTranslations\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DD322BC-097C-4B25-91BE-507A8731AA12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Raga-Bilawal_Jaaga-Uthe_Song_Br" sheetId="1" r:id="rId4"/>
+    <sheet name="Raga-Bilawal_Jaaga-Uthe_Song_Br" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="zhPhryGr3WYWLCgQOikyf8aU4X+5Zxr1KZW4D0JJt8c="/>
@@ -16,22 +25,30 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment authorId="0" ref="N35">
+    <comment ref="N35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
-        <t xml:space="preserve">======
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>======
 ID#AAAB2ALqDc0
 Virata Pusuluri    (2026-03-17 18:39:35)
 Ga+_ _ Ri+</t>
+        </r>
       </text>
     </comment>
   </commentList>
   <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
+    <ext xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mhQZ/BN1RlEeI9Q8bMhcqNoeIiBYA=="/>
     </ext>
   </extLst>
@@ -458,9 +475,6 @@
     <t>Ma+</t>
   </si>
   <si>
-    <t>Ga+ Ri+</t>
-  </si>
-  <si>
     <t>Sa+Ni</t>
   </si>
   <si>
@@ -636,15 +650,18 @@
   </si>
   <si>
     <t>la:</t>
+  </si>
+  <si>
+    <t>Ga+_ _Ri+</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="10">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -653,6 +670,7 @@
       <b/>
       <i/>
       <u/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -660,10 +678,12 @@
       <b/>
       <i/>
       <u/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -671,6 +691,7 @@
       <b/>
       <i/>
       <u/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -678,6 +699,7 @@
       <b/>
       <i/>
       <u/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -685,14 +707,19 @@
       <b/>
       <i/>
       <u/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
-    <font/>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
     <font>
       <b/>
       <i/>
       <u/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -700,6 +727,7 @@
       <b/>
       <i/>
       <u/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -709,11 +737,17 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="16">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -727,6 +761,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -738,6 +773,8 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -746,30 +783,38 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -779,27 +824,38 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -808,116 +864,150 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="27">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="10" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="11" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="13" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="14" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="14" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="15" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="15" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="11" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1107,21 +1197,24 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:Z1000"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="33.38"/>
-    <col customWidth="1" min="2" max="17" width="8.63"/>
+    <col min="1" max="1" width="33.42578125" customWidth="1"/>
+    <col min="2" max="17" width="8.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1151,7 +1244,7 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
+    <row r="2" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1179,7 +1272,7 @@
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
+    <row r="3" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -1209,7 +1302,7 @@
       <c r="Y3" s="3"/>
       <c r="Z3" s="3"/>
     </row>
-    <row r="4" ht="15.75" customHeight="1">
+    <row r="4" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
@@ -1239,7 +1332,7 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
+    <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -1267,7 +1360,7 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
     </row>
-    <row r="6" ht="15.75" customHeight="1">
+    <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
         <v>3</v>
       </c>
@@ -1297,7 +1390,7 @@
       <c r="Y6" s="7"/>
       <c r="Z6" s="8"/>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
+    <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -1325,38 +1418,38 @@
       <c r="Y7" s="3"/>
       <c r="Z7" s="3"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
+    <row r="8" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="11" t="s">
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="11" t="s">
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="I8" s="10"/>
-      <c r="J8" s="11" t="s">
+      <c r="I8" s="16"/>
+      <c r="J8" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="11" t="s">
+      <c r="K8" s="16"/>
+      <c r="L8" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="M8" s="10"/>
-      <c r="N8" s="11" t="s">
+      <c r="M8" s="16"/>
+      <c r="N8" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="O8" s="10"/>
-      <c r="P8" s="10"/>
-      <c r="Q8" s="12"/>
+      <c r="O8" s="16"/>
+      <c r="P8" s="16"/>
+      <c r="Q8" s="17"/>
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
       <c r="T8" s="3"/>
@@ -1367,29 +1460,38 @@
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="13" t="s">
+    <row r="9" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="I9" s="19"/>
+      <c r="J9" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="L9" s="3" t="s">
+      <c r="K9" s="19"/>
+      <c r="L9" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="N9" s="3" t="s">
+      <c r="M9" s="19"/>
+      <c r="N9" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="Q9" s="15"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="21"/>
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
       <c r="T9" s="3"/>
@@ -1400,29 +1502,38 @@
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="13" t="s">
+    <row r="10" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="I10" s="19"/>
+      <c r="J10" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="L10" s="3" t="s">
+      <c r="K10" s="19"/>
+      <c r="L10" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="N10" s="3" t="s">
+      <c r="M10" s="19"/>
+      <c r="N10" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="Q10" s="15"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="21"/>
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
       <c r="T10" s="3"/>
@@ -1433,29 +1544,38 @@
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="13" t="s">
+    <row r="11" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="I11" s="19"/>
+      <c r="J11" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="L11" s="3" t="s">
+      <c r="K11" s="19"/>
+      <c r="L11" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="N11" s="3" t="s">
+      <c r="M11" s="19"/>
+      <c r="N11" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="Q11" s="15"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="21"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
@@ -1466,22 +1586,24 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
     </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="13" t="s">
+    <row r="12" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="18" t="s">
         <v>33</v>
       </c>
+      <c r="C12" s="19"/>
       <c r="D12" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="20" t="s">
         <v>36</v>
       </c>
+      <c r="G12" s="19"/>
       <c r="H12" s="3" t="s">
         <v>37</v>
       </c>
@@ -1500,13 +1622,14 @@
       <c r="M12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="N12" s="3" t="s">
+      <c r="N12" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="P12" s="3" t="s">
+      <c r="O12" s="19"/>
+      <c r="P12" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="Q12" s="15"/>
+      <c r="Q12" s="21"/>
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
       <c r="T12" s="3"/>
@@ -1517,22 +1640,24 @@
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
     </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="13" t="s">
+    <row r="13" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="18" t="s">
         <v>45</v>
       </c>
+      <c r="C13" s="19"/>
       <c r="D13" s="3" t="s">
         <v>46</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="20" t="s">
         <v>48</v>
       </c>
+      <c r="G13" s="19"/>
       <c r="H13" s="3" t="s">
         <v>49</v>
       </c>
@@ -1551,13 +1676,14 @@
       <c r="M13" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="N13" s="3" t="s">
+      <c r="N13" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="P13" s="3" t="s">
+      <c r="O13" s="19"/>
+      <c r="P13" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="Q13" s="15"/>
+      <c r="Q13" s="21"/>
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
       <c r="T13" s="3"/>
@@ -1568,22 +1694,24 @@
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="13" t="s">
+    <row r="14" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="18" t="s">
         <v>57</v>
       </c>
+      <c r="C14" s="19"/>
       <c r="D14" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="20" t="s">
         <v>57</v>
       </c>
+      <c r="G14" s="19"/>
       <c r="H14" s="3" t="s">
         <v>58</v>
       </c>
@@ -1602,13 +1730,14 @@
       <c r="M14" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="N14" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="P14" s="3" t="s">
+      <c r="O14" s="19"/>
+      <c r="P14" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="Q14" s="15"/>
+      <c r="Q14" s="21"/>
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
       <c r="T14" s="3"/>
@@ -1619,54 +1748,54 @@
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
+    <row r="15" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="18" t="s">
+      <c r="C15" s="23"/>
+      <c r="D15" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="E15" s="18" t="s">
+      <c r="E15" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="F15" s="18" t="s">
+      <c r="F15" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="G15" s="18" t="s">
+      <c r="G15" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="H15" s="18" t="s">
+      <c r="H15" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="I15" s="18" t="s">
+      <c r="I15" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="J15" s="18" t="s">
+      <c r="J15" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="K15" s="18" t="s">
+      <c r="K15" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="L15" s="18" t="s">
+      <c r="L15" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="M15" s="18" t="s">
+      <c r="M15" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="N15" s="18" t="s">
+      <c r="N15" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="O15" s="18" t="s">
+      <c r="O15" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="P15" s="18" t="s">
+      <c r="P15" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="Q15" s="19"/>
+      <c r="Q15" s="25"/>
       <c r="R15" s="3"/>
       <c r="S15" s="3"/>
       <c r="T15" s="3"/>
@@ -1677,7 +1806,7 @@
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
+    <row r="16" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -1705,36 +1834,36 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
+    <row r="17" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="11" t="s">
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="G17" s="10"/>
-      <c r="H17" s="11" t="s">
+      <c r="G17" s="16"/>
+      <c r="H17" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I17" s="10"/>
-      <c r="J17" s="11" t="s">
+      <c r="I17" s="16"/>
+      <c r="J17" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="11" t="s">
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="N17" s="10"/>
-      <c r="O17" s="10"/>
-      <c r="P17" s="10"/>
-      <c r="Q17" s="12"/>
+      <c r="N17" s="16"/>
+      <c r="O17" s="16"/>
+      <c r="P17" s="16"/>
+      <c r="Q17" s="17"/>
       <c r="R17" s="3"/>
       <c r="S17" s="3"/>
       <c r="T17" s="3"/>
@@ -1745,26 +1874,36 @@
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="13" t="s">
+    <row r="18" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="G18" s="19"/>
+      <c r="H18" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="J18" s="3" t="s">
+      <c r="I18" s="19"/>
+      <c r="J18" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="M18" s="3" t="s">
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="Q18" s="15"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
+      <c r="P18" s="19"/>
+      <c r="Q18" s="21"/>
       <c r="R18" s="3"/>
       <c r="S18" s="3"/>
       <c r="T18" s="3"/>
@@ -1775,26 +1914,36 @@
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="13" t="s">
+    <row r="19" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="H19" s="3" t="s">
+      <c r="G19" s="19"/>
+      <c r="H19" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="J19" s="3" t="s">
+      <c r="I19" s="19"/>
+      <c r="J19" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="M19" s="3" t="s">
+      <c r="K19" s="19"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="Q19" s="15"/>
+      <c r="N19" s="19"/>
+      <c r="O19" s="19"/>
+      <c r="P19" s="19"/>
+      <c r="Q19" s="21"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
@@ -1805,26 +1954,36 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="13" t="s">
+    <row r="20" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="H20" s="3" t="s">
+      <c r="G20" s="19"/>
+      <c r="H20" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="I20" s="19"/>
+      <c r="J20" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="M20" s="3" t="s">
+      <c r="K20" s="19"/>
+      <c r="L20" s="19"/>
+      <c r="M20" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="Q20" s="15"/>
+      <c r="N20" s="19"/>
+      <c r="O20" s="19"/>
+      <c r="P20" s="19"/>
+      <c r="Q20" s="21"/>
       <c r="R20" s="3"/>
       <c r="S20" s="3"/>
       <c r="T20" s="3"/>
@@ -1835,44 +1994,48 @@
       <c r="Y20" s="3"/>
       <c r="Z20" s="3"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="13" t="s">
+    <row r="21" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="20" t="s">
         <v>87</v>
       </c>
+      <c r="C21" s="19"/>
       <c r="D21" s="3" t="s">
         <v>88</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="20" t="s">
         <v>68</v>
       </c>
+      <c r="G21" s="19"/>
       <c r="H21" s="3" t="s">
         <v>89</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="J21" s="20" t="s">
         <v>91</v>
       </c>
+      <c r="K21" s="19"/>
       <c r="L21" s="3" t="s">
         <v>92</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="N21" s="3" t="s">
+      <c r="N21" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="P21" s="3" t="s">
+      <c r="O21" s="19"/>
+      <c r="P21" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="Q21" s="15"/>
+      <c r="Q21" s="21"/>
       <c r="R21" s="3"/>
       <c r="S21" s="3"/>
       <c r="T21" s="3"/>
@@ -1883,44 +2046,48 @@
       <c r="Y21" s="3"/>
       <c r="Z21" s="3"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="13" t="s">
+    <row r="22" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="20" t="s">
         <v>94</v>
       </c>
+      <c r="C22" s="19"/>
       <c r="D22" s="3" t="s">
         <v>95</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F22" s="20" t="s">
         <v>73</v>
       </c>
+      <c r="G22" s="19"/>
       <c r="H22" s="3" t="s">
         <v>96</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="J22" s="20" t="s">
         <v>98</v>
       </c>
+      <c r="K22" s="19"/>
       <c r="L22" s="3" t="s">
         <v>99</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="N22" s="3" t="s">
+      <c r="N22" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="P22" s="3" t="s">
+      <c r="O22" s="19"/>
+      <c r="P22" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="Q22" s="15"/>
+      <c r="Q22" s="21"/>
       <c r="R22" s="3"/>
       <c r="S22" s="3"/>
       <c r="T22" s="3"/>
@@ -1931,44 +2098,48 @@
       <c r="Y22" s="3"/>
       <c r="Z22" s="3"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="13" t="s">
+    <row r="23" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="20" t="s">
         <v>57</v>
       </c>
+      <c r="C23" s="19"/>
       <c r="D23" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="F23" s="20" t="s">
         <v>57</v>
       </c>
+      <c r="G23" s="19"/>
       <c r="H23" s="3" t="s">
         <v>58</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="J23" s="3" t="s">
+      <c r="J23" s="20" t="s">
         <v>57</v>
       </c>
+      <c r="K23" s="19"/>
       <c r="L23" s="3" t="s">
         <v>58</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="N23" s="3" t="s">
+      <c r="N23" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="P23" s="3" t="s">
+      <c r="O23" s="19"/>
+      <c r="P23" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="Q23" s="15"/>
+      <c r="Q23" s="21"/>
       <c r="R23" s="3"/>
       <c r="S23" s="3"/>
       <c r="T23" s="3"/>
@@ -1979,50 +2150,50 @@
       <c r="Y23" s="3"/>
       <c r="Z23" s="3"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="C24" s="17"/>
-      <c r="D24" s="18" t="s">
+      <c r="C24" s="23"/>
+      <c r="D24" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E24" s="18" t="s">
+      <c r="E24" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="F24" s="18" t="s">
+      <c r="F24" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="G24" s="17"/>
-      <c r="H24" s="18" t="s">
+      <c r="G24" s="23"/>
+      <c r="H24" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="I24" s="18" t="s">
+      <c r="I24" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="J24" s="18" t="s">
+      <c r="J24" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="K24" s="17"/>
-      <c r="L24" s="18" t="s">
+      <c r="K24" s="23"/>
+      <c r="L24" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="M24" s="18" t="s">
+      <c r="M24" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="N24" s="18" t="s">
+      <c r="N24" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="O24" s="18" t="s">
+      <c r="O24" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="P24" s="18" t="s">
+      <c r="P24" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="Q24" s="20" t="s">
+      <c r="Q24" s="12" t="s">
         <v>109</v>
       </c>
       <c r="R24" s="3"/>
@@ -2035,7 +2206,7 @@
       <c r="Y24" s="3"/>
       <c r="Z24" s="3"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -2063,7 +2234,7 @@
       <c r="Y25" s="3"/>
       <c r="Z25" s="3"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
         <v>110</v>
       </c>
@@ -2093,7 +2264,7 @@
       <c r="Y26" s="7"/>
       <c r="Z26" s="8"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6"/>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
@@ -2121,36 +2292,36 @@
       <c r="Y27" s="7"/>
       <c r="Z27" s="8"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B28" s="11" t="s">
+      <c r="B28" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="11" t="s">
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="11" t="s">
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="I28" s="10"/>
-      <c r="J28" s="11" t="s">
+      <c r="I28" s="16"/>
+      <c r="J28" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="K28" s="10"/>
-      <c r="L28" s="10"/>
-      <c r="M28" s="11" t="s">
+      <c r="K28" s="16"/>
+      <c r="L28" s="16"/>
+      <c r="M28" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="N28" s="10"/>
-      <c r="O28" s="10"/>
-      <c r="P28" s="10"/>
-      <c r="Q28" s="12"/>
+      <c r="N28" s="16"/>
+      <c r="O28" s="16"/>
+      <c r="P28" s="16"/>
+      <c r="Q28" s="17"/>
       <c r="R28" s="3"/>
       <c r="S28" s="3"/>
       <c r="T28" s="3"/>
@@ -2161,26 +2332,36 @@
       <c r="Y28" s="3"/>
       <c r="Z28" s="3"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="13" t="s">
+    <row r="29" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="H29" s="3" t="s">
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="J29" s="3" t="s">
+      <c r="I29" s="19"/>
+      <c r="J29" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="M29" s="3" t="s">
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="Q29" s="15"/>
+      <c r="N29" s="19"/>
+      <c r="O29" s="19"/>
+      <c r="P29" s="19"/>
+      <c r="Q29" s="21"/>
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
       <c r="T29" s="3"/>
@@ -2191,26 +2372,36 @@
       <c r="Y29" s="3"/>
       <c r="Z29" s="3"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="13" t="s">
+    <row r="30" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="H30" s="3" t="s">
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="J30" s="3" t="s">
+      <c r="I30" s="19"/>
+      <c r="J30" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="M30" s="3" t="s">
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
+      <c r="M30" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="Q30" s="15"/>
+      <c r="N30" s="19"/>
+      <c r="O30" s="19"/>
+      <c r="P30" s="19"/>
+      <c r="Q30" s="21"/>
       <c r="R30" s="3"/>
       <c r="S30" s="3"/>
       <c r="T30" s="3"/>
@@ -2221,26 +2412,36 @@
       <c r="Y30" s="3"/>
       <c r="Z30" s="3"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="13" t="s">
+    <row r="31" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="H31" s="3" t="s">
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="J31" s="3" t="s">
+      <c r="I31" s="19"/>
+      <c r="J31" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="M31" s="3" t="s">
+      <c r="K31" s="19"/>
+      <c r="L31" s="19"/>
+      <c r="M31" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="Q31" s="15"/>
+      <c r="N31" s="19"/>
+      <c r="O31" s="19"/>
+      <c r="P31" s="19"/>
+      <c r="Q31" s="21"/>
       <c r="R31" s="3"/>
       <c r="S31" s="3"/>
       <c r="T31" s="3"/>
@@ -2251,19 +2452,21 @@
       <c r="Y31" s="3"/>
       <c r="Z31" s="3"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="13" t="s">
+    <row r="32" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="20" t="s">
         <v>126</v>
       </c>
+      <c r="C32" s="19"/>
       <c r="D32" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="E32" s="20" t="s">
         <v>91</v>
       </c>
+      <c r="F32" s="19"/>
       <c r="G32" s="3" t="s">
         <v>92</v>
       </c>
@@ -2273,22 +2476,24 @@
       <c r="I32" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="J32" s="3" t="s">
+      <c r="J32" s="20" t="s">
         <v>87</v>
       </c>
+      <c r="K32" s="19"/>
       <c r="L32" s="3" t="s">
         <v>88</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="N32" s="3" t="s">
+      <c r="N32" s="20" t="s">
         <v>127</v>
       </c>
+      <c r="O32" s="19"/>
       <c r="P32" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="Q32" s="21" t="s">
+      <c r="Q32" s="13" t="s">
         <v>128</v>
       </c>
       <c r="R32" s="3"/>
@@ -2301,19 +2506,21 @@
       <c r="Y32" s="3"/>
       <c r="Z32" s="3"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="13" t="s">
+    <row r="33" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="20" t="s">
         <v>129</v>
       </c>
+      <c r="C33" s="19"/>
       <c r="D33" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="E33" s="20" t="s">
         <v>98</v>
       </c>
+      <c r="F33" s="19"/>
       <c r="G33" s="3" t="s">
         <v>130</v>
       </c>
@@ -2323,22 +2530,24 @@
       <c r="I33" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="J33" s="3" t="s">
+      <c r="J33" s="20" t="s">
         <v>94</v>
       </c>
+      <c r="K33" s="19"/>
       <c r="L33" s="3" t="s">
         <v>131</v>
       </c>
       <c r="M33" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="N33" s="3" t="s">
+      <c r="N33" s="20" t="s">
         <v>132</v>
       </c>
+      <c r="O33" s="19"/>
       <c r="P33" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="Q33" s="21" t="s">
+      <c r="Q33" s="13" t="s">
         <v>134</v>
       </c>
       <c r="R33" s="3"/>
@@ -2351,19 +2560,21 @@
       <c r="Y33" s="3"/>
       <c r="Z33" s="3"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="13" t="s">
+    <row r="34" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="20" t="s">
         <v>57</v>
       </c>
+      <c r="C34" s="19"/>
       <c r="D34" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="E34" s="20" t="s">
         <v>57</v>
       </c>
+      <c r="F34" s="19"/>
       <c r="G34" s="3" t="s">
         <v>58</v>
       </c>
@@ -2373,22 +2584,24 @@
       <c r="I34" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="J34" s="3" t="s">
+      <c r="J34" s="20" t="s">
         <v>57</v>
       </c>
+      <c r="K34" s="19"/>
       <c r="L34" s="3" t="s">
         <v>58</v>
       </c>
       <c r="M34" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="N34" s="3" t="s">
+      <c r="N34" s="20" t="s">
         <v>57</v>
       </c>
+      <c r="O34" s="19"/>
       <c r="P34" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="Q34" s="21" t="s">
+      <c r="Q34" s="13" t="s">
         <v>58</v>
       </c>
       <c r="R34" s="3"/>
@@ -2401,48 +2614,48 @@
       <c r="Y34" s="3"/>
       <c r="Z34" s="3"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
+    <row r="35" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B35" s="18" t="s">
+      <c r="B35" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="C35" s="17"/>
-      <c r="D35" s="18" t="s">
+      <c r="C35" s="23"/>
+      <c r="D35" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="E35" s="18" t="s">
+      <c r="E35" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="F35" s="17"/>
-      <c r="G35" s="18" t="s">
+      <c r="F35" s="23"/>
+      <c r="G35" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="H35" s="18" t="s">
+      <c r="H35" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="I35" s="18" t="s">
+      <c r="I35" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="J35" s="18" t="s">
+      <c r="J35" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="K35" s="17"/>
-      <c r="L35" s="18" t="s">
+      <c r="K35" s="23"/>
+      <c r="L35" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="M35" s="18" t="s">
+      <c r="M35" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="N35" s="18" t="s">
+      <c r="N35" s="24" t="s">
+        <v>198</v>
+      </c>
+      <c r="O35" s="23"/>
+      <c r="P35" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="O35" s="17"/>
-      <c r="P35" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="Q35" s="20" t="s">
+      <c r="Q35" s="12" t="s">
         <v>60</v>
       </c>
       <c r="R35" s="3"/>
@@ -2455,7 +2668,7 @@
       <c r="Y35" s="3"/>
       <c r="Z35" s="3"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
+    <row r="36" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -2483,35 +2696,35 @@
       <c r="Y36" s="3"/>
       <c r="Z36" s="3"/>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
+    <row r="37" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B37" s="11" t="s">
+      <c r="B37" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="C37" s="16"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="11" t="s">
+      <c r="G37" s="16"/>
+      <c r="H37" s="16"/>
+      <c r="I37" s="16"/>
+      <c r="J37" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="10"/>
-      <c r="J37" s="11" t="s">
+      <c r="K37" s="16"/>
+      <c r="L37" s="16"/>
+      <c r="M37" s="16"/>
+      <c r="N37" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="K37" s="10"/>
-      <c r="L37" s="10"/>
-      <c r="M37" s="10"/>
-      <c r="N37" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="O37" s="10"/>
-      <c r="P37" s="10"/>
-      <c r="Q37" s="12"/>
-      <c r="R37" s="11"/>
+      <c r="O37" s="16"/>
+      <c r="P37" s="16"/>
+      <c r="Q37" s="17"/>
+      <c r="R37" s="9"/>
       <c r="S37" s="3"/>
       <c r="T37" s="3"/>
       <c r="U37" s="3"/>
@@ -2521,23 +2734,34 @@
       <c r="Y37" s="3"/>
       <c r="Z37" s="3"/>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="13" t="s">
+    <row r="38" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="F38" s="3" t="s">
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="J38" s="3" t="s">
+      <c r="K38" s="19"/>
+      <c r="L38" s="19"/>
+      <c r="M38" s="19"/>
+      <c r="N38" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="N38" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q38" s="15"/>
+      <c r="O38" s="19"/>
+      <c r="P38" s="19"/>
+      <c r="Q38" s="21"/>
       <c r="R38" s="3"/>
       <c r="S38" s="3"/>
       <c r="T38" s="3"/>
@@ -2548,23 +2772,34 @@
       <c r="Y38" s="3"/>
       <c r="Z38" s="3"/>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="13" t="s">
+    <row r="39" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="F39" s="3" t="s">
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="J39" s="3" t="s">
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
+      <c r="M39" s="19"/>
+      <c r="N39" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="N39" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="Q39" s="15"/>
+      <c r="O39" s="19"/>
+      <c r="P39" s="19"/>
+      <c r="Q39" s="21"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
@@ -2575,23 +2810,34 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="13" t="s">
+    <row r="40" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="C40" s="19"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="F40" s="3" t="s">
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="J40" s="3" t="s">
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="N40" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q40" s="15"/>
+      <c r="O40" s="19"/>
+      <c r="P40" s="19"/>
+      <c r="Q40" s="21"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
@@ -2602,44 +2848,48 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="13" t="s">
+    <row r="41" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="10" t="s">
         <v>32</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>41</v>
       </c>
       <c r="C41" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D41" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="E41" s="19"/>
+      <c r="F41" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>159</v>
-      </c>
+      <c r="G41" s="19"/>
       <c r="H41" s="3" t="s">
         <v>90</v>
       </c>
       <c r="I41" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="J41" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>161</v>
-      </c>
+      <c r="K41" s="19"/>
       <c r="L41" s="3" t="s">
         <v>38</v>
       </c>
       <c r="M41" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>162</v>
-      </c>
+      <c r="N41" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="O41" s="19"/>
       <c r="P41" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="Q41" s="21" t="s">
+      <c r="Q41" s="13" t="s">
         <v>128</v>
       </c>
       <c r="R41" s="3"/>
@@ -2652,44 +2902,48 @@
       <c r="Y41" s="3"/>
       <c r="Z41" s="3"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="13" t="s">
+    <row r="42" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="10" t="s">
         <v>44</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C42" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D42" s="20" t="s">
         <v>163</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="E42" s="19"/>
+      <c r="F42" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="F42" s="3" t="s">
-        <v>165</v>
-      </c>
+      <c r="G42" s="19"/>
       <c r="H42" s="3" t="s">
         <v>97</v>
       </c>
       <c r="I42" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="J42" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>167</v>
-      </c>
+      <c r="K42" s="19"/>
       <c r="L42" s="3" t="s">
         <v>133</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>168</v>
-      </c>
+      <c r="N42" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="O42" s="19"/>
       <c r="P42" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="Q42" s="21" t="s">
+      <c r="Q42" s="13" t="s">
         <v>134</v>
       </c>
       <c r="R42" s="3"/>
@@ -2702,8 +2956,8 @@
       <c r="Y42" s="3"/>
       <c r="Z42" s="3"/>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="13" t="s">
+    <row r="43" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="10" t="s">
         <v>56</v>
       </c>
       <c r="B43" s="3" t="s">
@@ -2712,34 +2966,38 @@
       <c r="C43" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="D43" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="F43" s="3" t="s">
+      <c r="E43" s="19"/>
+      <c r="F43" s="20" t="s">
         <v>57</v>
       </c>
+      <c r="G43" s="19"/>
       <c r="H43" s="3" t="s">
         <v>58</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="J43" s="3" t="s">
+      <c r="J43" s="20" t="s">
         <v>57</v>
       </c>
+      <c r="K43" s="19"/>
       <c r="L43" s="3" t="s">
         <v>58</v>
       </c>
       <c r="M43" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="N43" s="3" t="s">
+      <c r="N43" s="20" t="s">
         <v>57</v>
       </c>
+      <c r="O43" s="19"/>
       <c r="P43" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="Q43" s="21" t="s">
+      <c r="Q43" s="13" t="s">
         <v>58</v>
       </c>
       <c r="R43" s="3"/>
@@ -2752,54 +3010,54 @@
       <c r="Y43" s="3"/>
       <c r="Z43" s="3"/>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
+    <row r="44" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B44" s="18" t="s">
+      <c r="B44" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="C44" s="18" t="s">
+      <c r="C44" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="D44" s="18" t="s">
+      <c r="D44" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="E44" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="E44" s="18" t="s">
+      <c r="F44" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="G44" s="23"/>
+      <c r="H44" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="I44" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="J44" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="K44" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="F44" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="G44" s="17"/>
-      <c r="H44" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="I44" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="J44" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="K44" s="18" t="s">
+      <c r="L44" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="M44" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="N44" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="L44" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="M44" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="N44" s="18" t="s">
+      <c r="O44" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="O44" s="18" t="s">
-        <v>173</v>
-      </c>
-      <c r="P44" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="Q44" s="20" t="s">
+      <c r="P44" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q44" s="12" t="s">
         <v>60</v>
       </c>
       <c r="R44" s="3"/>
@@ -2812,8 +3070,8 @@
       <c r="Y44" s="3"/>
       <c r="Z44" s="3"/>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="22"/>
+    <row r="45" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="14"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
@@ -2829,7 +3087,7 @@
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
       <c r="P45" s="3"/>
-      <c r="Q45" s="21"/>
+      <c r="Q45" s="13"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3"/>
       <c r="T45" s="3"/>
@@ -2840,36 +3098,36 @@
       <c r="Y45" s="3"/>
       <c r="Z45" s="3"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
+    <row r="46" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B46" s="11" t="s">
+      <c r="B46" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="C46" s="16"/>
+      <c r="D46" s="16"/>
+      <c r="E46" s="16"/>
+      <c r="F46" s="16"/>
+      <c r="G46" s="16"/>
+      <c r="H46" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="C46" s="10"/>
-      <c r="D46" s="10"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="10"/>
-      <c r="G46" s="10"/>
-      <c r="H46" s="11" t="s">
+      <c r="I46" s="16"/>
+      <c r="J46" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="K46" s="16"/>
+      <c r="L46" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="I46" s="10"/>
-      <c r="J46" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="K46" s="10"/>
-      <c r="L46" s="11" t="s">
+      <c r="M46" s="16"/>
+      <c r="N46" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="M46" s="10"/>
-      <c r="N46" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="O46" s="10"/>
-      <c r="P46" s="10"/>
-      <c r="Q46" s="12"/>
+      <c r="O46" s="16"/>
+      <c r="P46" s="16"/>
+      <c r="Q46" s="17"/>
       <c r="R46" s="3"/>
       <c r="S46" s="3"/>
       <c r="T46" s="3"/>
@@ -2880,26 +3138,36 @@
       <c r="Y46" s="3"/>
       <c r="Z46" s="3"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="13" t="s">
+    <row r="47" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="C47" s="19"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="19"/>
+      <c r="F47" s="19"/>
+      <c r="G47" s="19"/>
+      <c r="H47" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="H47" s="3" t="s">
+      <c r="I47" s="19"/>
+      <c r="J47" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="K47" s="19"/>
+      <c r="L47" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L47" s="3" t="s">
+      <c r="M47" s="19"/>
+      <c r="N47" s="20" t="s">
         <v>180</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q47" s="15"/>
+      <c r="O47" s="19"/>
+      <c r="P47" s="19"/>
+      <c r="Q47" s="21"/>
       <c r="R47" s="3"/>
       <c r="S47" s="3"/>
       <c r="T47" s="3"/>
@@ -2910,26 +3178,36 @@
       <c r="Y47" s="3"/>
       <c r="Z47" s="3"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="13" t="s">
+    <row r="48" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="C48" s="19"/>
+      <c r="D48" s="19"/>
+      <c r="E48" s="19"/>
+      <c r="F48" s="19"/>
+      <c r="G48" s="19"/>
+      <c r="H48" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="H48" s="3" t="s">
+      <c r="I48" s="19"/>
+      <c r="J48" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="K48" s="19"/>
+      <c r="L48" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L48" s="3" t="s">
+      <c r="M48" s="19"/>
+      <c r="N48" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q48" s="15"/>
+      <c r="O48" s="19"/>
+      <c r="P48" s="19"/>
+      <c r="Q48" s="21"/>
       <c r="R48" s="3"/>
       <c r="S48" s="3"/>
       <c r="T48" s="3"/>
@@ -2940,26 +3218,36 @@
       <c r="Y48" s="3"/>
       <c r="Z48" s="3"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="13" t="s">
+    <row r="49" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="C49" s="19"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="19"/>
+      <c r="F49" s="19"/>
+      <c r="G49" s="19"/>
+      <c r="H49" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="H49" s="3" t="s">
+      <c r="I49" s="19"/>
+      <c r="J49" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K49" s="19"/>
+      <c r="L49" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L49" s="3" t="s">
+      <c r="M49" s="19"/>
+      <c r="N49" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q49" s="15"/>
+      <c r="O49" s="19"/>
+      <c r="P49" s="19"/>
+      <c r="Q49" s="21"/>
       <c r="R49" s="3"/>
       <c r="S49" s="3"/>
       <c r="T49" s="3"/>
@@ -2970,19 +3258,21 @@
       <c r="Y49" s="3"/>
       <c r="Z49" s="3"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="13" t="s">
+    <row r="50" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="10" t="s">
         <v>32</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C50" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="D50" s="19"/>
+      <c r="E50" s="20" t="s">
         <v>190</v>
       </c>
-      <c r="E50" s="3" t="s">
-        <v>191</v>
-      </c>
+      <c r="F50" s="19"/>
       <c r="G50" s="3" t="s">
         <v>34</v>
       </c>
@@ -2998,15 +3288,18 @@
       <c r="K50" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L50" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="N50" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="P50" s="3" t="s">
+      <c r="L50" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="M50" s="19"/>
+      <c r="N50" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="O50" s="19"/>
+      <c r="P50" s="20" t="s">
         <v>43</v>
       </c>
+      <c r="Q50" s="19"/>
       <c r="R50" s="3"/>
       <c r="S50" s="3"/>
       <c r="T50" s="3"/>
@@ -3017,27 +3310,29 @@
       <c r="Y50" s="3"/>
       <c r="Z50" s="3"/>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="13" t="s">
+    <row r="51" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="10" t="s">
         <v>44</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C51" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="D51" s="19"/>
+      <c r="E51" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="E51" s="3" t="s">
+      <c r="F51" s="19"/>
+      <c r="G51" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="G51" s="3" t="s">
+      <c r="H51" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="H51" s="3" t="s">
+      <c r="I51" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>197</v>
       </c>
       <c r="J51" s="3" t="s">
         <v>53</v>
@@ -3045,16 +3340,18 @@
       <c r="K51" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="L51" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="N51" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="P51" s="3" t="s">
+      <c r="L51" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="M51" s="19"/>
+      <c r="N51" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="O51" s="19"/>
+      <c r="P51" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="Q51" s="15"/>
+      <c r="Q51" s="21"/>
       <c r="R51" s="3"/>
       <c r="S51" s="3"/>
       <c r="T51" s="3"/>
@@ -3065,19 +3362,21 @@
       <c r="Y51" s="3"/>
       <c r="Z51" s="3"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="13" t="s">
+    <row r="52" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="10" t="s">
         <v>56</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C52" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="E52" s="3" t="s">
+      <c r="D52" s="19"/>
+      <c r="E52" s="20" t="s">
         <v>57</v>
       </c>
+      <c r="F52" s="19"/>
       <c r="G52" s="3" t="s">
         <v>58</v>
       </c>
@@ -3093,16 +3392,18 @@
       <c r="K52" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="L52" s="3" t="s">
+      <c r="L52" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="N52" s="3" t="s">
+      <c r="M52" s="19"/>
+      <c r="N52" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="P52" s="3" t="s">
+      <c r="O52" s="19"/>
+      <c r="P52" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="Q52" s="15"/>
+      <c r="Q52" s="21"/>
       <c r="R52" s="3"/>
       <c r="S52" s="3"/>
       <c r="T52" s="3"/>
@@ -3113,54 +3414,54 @@
       <c r="Y52" s="3"/>
       <c r="Z52" s="3"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
+    <row r="53" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B53" s="18" t="s">
+      <c r="B53" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="C53" s="18" t="s">
+      <c r="C53" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="D53" s="18" t="s">
+      <c r="D53" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="E53" s="18" t="s">
+      <c r="E53" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="F53" s="18" t="s">
+      <c r="F53" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="G53" s="18" t="s">
+      <c r="G53" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="H53" s="18" t="s">
+      <c r="H53" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="I53" s="18" t="s">
+      <c r="I53" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="J53" s="18" t="s">
+      <c r="J53" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="K53" s="18" t="s">
+      <c r="K53" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="L53" s="18" t="s">
+      <c r="L53" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="M53" s="17"/>
-      <c r="N53" s="18" t="s">
+      <c r="M53" s="23"/>
+      <c r="N53" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="O53" s="18" t="s">
+      <c r="O53" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="P53" s="18" t="s">
+      <c r="P53" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="Q53" s="20" t="s">
+      <c r="Q53" s="12" t="s">
         <v>109</v>
       </c>
       <c r="R53" s="3"/>
@@ -3173,7 +3474,7 @@
       <c r="Y53" s="3"/>
       <c r="Z53" s="3"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
+    <row r="54" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -3201,7 +3502,7 @@
       <c r="Y54" s="3"/>
       <c r="Z54" s="3"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
+    <row r="55" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -3229,7 +3530,7 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
+    <row r="56" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -3257,7 +3558,7 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
+    <row r="57" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -3285,7 +3586,7 @@
       <c r="Y57" s="3"/>
       <c r="Z57" s="3"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
+    <row r="58" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -3313,7 +3614,7 @@
       <c r="Y58" s="3"/>
       <c r="Z58" s="3"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
+    <row r="59" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -3341,7 +3642,7 @@
       <c r="Y59" s="3"/>
       <c r="Z59" s="3"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
+    <row r="60" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -3369,7 +3670,7 @@
       <c r="Y60" s="3"/>
       <c r="Z60" s="3"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
+    <row r="61" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -3397,7 +3698,7 @@
       <c r="Y61" s="3"/>
       <c r="Z61" s="3"/>
     </row>
-    <row r="62" ht="15.75" customHeight="1">
+    <row r="62" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -3425,7 +3726,7 @@
       <c r="Y62" s="3"/>
       <c r="Z62" s="3"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
+    <row r="63" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -3453,7 +3754,7 @@
       <c r="Y63" s="3"/>
       <c r="Z63" s="3"/>
     </row>
-    <row r="64" ht="15.75" customHeight="1">
+    <row r="64" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
@@ -3481,7 +3782,7 @@
       <c r="Y64" s="3"/>
       <c r="Z64" s="3"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1">
+    <row r="65" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
@@ -3509,7 +3810,7 @@
       <c r="Y65" s="3"/>
       <c r="Z65" s="3"/>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
+    <row r="66" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
@@ -3537,7 +3838,7 @@
       <c r="Y66" s="3"/>
       <c r="Z66" s="3"/>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
+    <row r="67" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
@@ -3565,7 +3866,7 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
     </row>
-    <row r="68" ht="15.75" customHeight="1">
+    <row r="68" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
@@ -3593,7 +3894,7 @@
       <c r="Y68" s="3"/>
       <c r="Z68" s="3"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1">
+    <row r="69" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
@@ -3621,7 +3922,7 @@
       <c r="Y69" s="3"/>
       <c r="Z69" s="3"/>
     </row>
-    <row r="70" ht="15.75" customHeight="1">
+    <row r="70" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
@@ -3649,7 +3950,7 @@
       <c r="Y70" s="3"/>
       <c r="Z70" s="3"/>
     </row>
-    <row r="71" ht="15.75" customHeight="1">
+    <row r="71" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="2"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
@@ -3677,7 +3978,7 @@
       <c r="Y71" s="3"/>
       <c r="Z71" s="3"/>
     </row>
-    <row r="72" ht="15.75" customHeight="1">
+    <row r="72" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="2"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
@@ -3705,7 +4006,7 @@
       <c r="Y72" s="3"/>
       <c r="Z72" s="3"/>
     </row>
-    <row r="73" ht="15.75" customHeight="1">
+    <row r="73" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="2"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
@@ -3733,7 +4034,7 @@
       <c r="Y73" s="3"/>
       <c r="Z73" s="3"/>
     </row>
-    <row r="74" ht="15.75" customHeight="1">
+    <row r="74" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="2"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
@@ -3761,7 +4062,7 @@
       <c r="Y74" s="3"/>
       <c r="Z74" s="3"/>
     </row>
-    <row r="75" ht="15.75" customHeight="1">
+    <row r="75" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="2"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
@@ -3789,7 +4090,7 @@
       <c r="Y75" s="3"/>
       <c r="Z75" s="3"/>
     </row>
-    <row r="76" ht="15.75" customHeight="1">
+    <row r="76" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="2"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
@@ -3817,7 +4118,7 @@
       <c r="Y76" s="3"/>
       <c r="Z76" s="3"/>
     </row>
-    <row r="77" ht="15.75" customHeight="1">
+    <row r="77" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="2"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -3845,7 +4146,7 @@
       <c r="Y77" s="3"/>
       <c r="Z77" s="3"/>
     </row>
-    <row r="78" ht="15.75" customHeight="1">
+    <row r="78" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="2"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
@@ -3873,7 +4174,7 @@
       <c r="Y78" s="3"/>
       <c r="Z78" s="3"/>
     </row>
-    <row r="79" ht="15.75" customHeight="1">
+    <row r="79" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="2"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
@@ -3901,7 +4202,7 @@
       <c r="Y79" s="3"/>
       <c r="Z79" s="3"/>
     </row>
-    <row r="80" ht="15.75" customHeight="1">
+    <row r="80" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="2"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
@@ -3929,7 +4230,7 @@
       <c r="Y80" s="3"/>
       <c r="Z80" s="3"/>
     </row>
-    <row r="81" ht="15.75" customHeight="1">
+    <row r="81" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="2"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
@@ -3957,7 +4258,7 @@
       <c r="Y81" s="3"/>
       <c r="Z81" s="3"/>
     </row>
-    <row r="82" ht="15.75" customHeight="1">
+    <row r="82" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="2"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
@@ -3985,7 +4286,7 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
     </row>
-    <row r="83" ht="15.75" customHeight="1">
+    <row r="83" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="2"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
@@ -4013,7 +4314,7 @@
       <c r="Y83" s="3"/>
       <c r="Z83" s="3"/>
     </row>
-    <row r="84" ht="15.75" customHeight="1">
+    <row r="84" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="2"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
@@ -4041,7 +4342,7 @@
       <c r="Y84" s="3"/>
       <c r="Z84" s="3"/>
     </row>
-    <row r="85" ht="15.75" customHeight="1">
+    <row r="85" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="2"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
@@ -4069,7 +4370,7 @@
       <c r="Y85" s="3"/>
       <c r="Z85" s="3"/>
     </row>
-    <row r="86" ht="15.75" customHeight="1">
+    <row r="86" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="2"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
@@ -4097,7 +4398,7 @@
       <c r="Y86" s="3"/>
       <c r="Z86" s="3"/>
     </row>
-    <row r="87" ht="15.75" customHeight="1">
+    <row r="87" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="2"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
@@ -4125,7 +4426,7 @@
       <c r="Y87" s="3"/>
       <c r="Z87" s="3"/>
     </row>
-    <row r="88" ht="15.75" customHeight="1">
+    <row r="88" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="2"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
@@ -4153,7 +4454,7 @@
       <c r="Y88" s="3"/>
       <c r="Z88" s="3"/>
     </row>
-    <row r="89" ht="15.75" customHeight="1">
+    <row r="89" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="2"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
@@ -4181,7 +4482,7 @@
       <c r="Y89" s="3"/>
       <c r="Z89" s="3"/>
     </row>
-    <row r="90" ht="15.75" customHeight="1">
+    <row r="90" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="2"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
@@ -4209,7 +4510,7 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
     </row>
-    <row r="91" ht="15.75" customHeight="1">
+    <row r="91" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="2"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
@@ -4237,7 +4538,7 @@
       <c r="Y91" s="3"/>
       <c r="Z91" s="3"/>
     </row>
-    <row r="92" ht="15.75" customHeight="1">
+    <row r="92" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="2"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
@@ -4265,7 +4566,7 @@
       <c r="Y92" s="3"/>
       <c r="Z92" s="3"/>
     </row>
-    <row r="93" ht="15.75" customHeight="1">
+    <row r="93" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="2"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
@@ -4293,7 +4594,7 @@
       <c r="Y93" s="3"/>
       <c r="Z93" s="3"/>
     </row>
-    <row r="94" ht="15.75" customHeight="1">
+    <row r="94" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="2"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
@@ -4321,7 +4622,7 @@
       <c r="Y94" s="3"/>
       <c r="Z94" s="3"/>
     </row>
-    <row r="95" ht="15.75" customHeight="1">
+    <row r="95" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="2"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
@@ -4349,7 +4650,7 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
     </row>
-    <row r="96" ht="15.75" customHeight="1">
+    <row r="96" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="2"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
@@ -4377,7 +4678,7 @@
       <c r="Y96" s="3"/>
       <c r="Z96" s="3"/>
     </row>
-    <row r="97" ht="15.75" customHeight="1">
+    <row r="97" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="2"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
@@ -4405,7 +4706,7 @@
       <c r="Y97" s="3"/>
       <c r="Z97" s="3"/>
     </row>
-    <row r="98" ht="15.75" customHeight="1">
+    <row r="98" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="2"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
@@ -4433,7 +4734,7 @@
       <c r="Y98" s="3"/>
       <c r="Z98" s="3"/>
     </row>
-    <row r="99" ht="15.75" customHeight="1">
+    <row r="99" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="2"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
@@ -4461,7 +4762,7 @@
       <c r="Y99" s="3"/>
       <c r="Z99" s="3"/>
     </row>
-    <row r="100" ht="15.75" customHeight="1">
+    <row r="100" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="2"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
@@ -4489,7 +4790,7 @@
       <c r="Y100" s="3"/>
       <c r="Z100" s="3"/>
     </row>
-    <row r="101" ht="15.75" customHeight="1">
+    <row r="101" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="2"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -4517,7 +4818,7 @@
       <c r="Y101" s="3"/>
       <c r="Z101" s="3"/>
     </row>
-    <row r="102" ht="15.75" customHeight="1">
+    <row r="102" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="2"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
@@ -4545,7 +4846,7 @@
       <c r="Y102" s="3"/>
       <c r="Z102" s="3"/>
     </row>
-    <row r="103" ht="15.75" customHeight="1">
+    <row r="103" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="2"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
@@ -4573,7 +4874,7 @@
       <c r="Y103" s="3"/>
       <c r="Z103" s="3"/>
     </row>
-    <row r="104" ht="15.75" customHeight="1">
+    <row r="104" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="2"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
@@ -4601,7 +4902,7 @@
       <c r="Y104" s="3"/>
       <c r="Z104" s="3"/>
     </row>
-    <row r="105" ht="15.75" customHeight="1">
+    <row r="105" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="2"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
@@ -4629,7 +4930,7 @@
       <c r="Y105" s="3"/>
       <c r="Z105" s="3"/>
     </row>
-    <row r="106" ht="15.75" customHeight="1">
+    <row r="106" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="2"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
@@ -4657,7 +4958,7 @@
       <c r="Y106" s="3"/>
       <c r="Z106" s="3"/>
     </row>
-    <row r="107" ht="15.75" customHeight="1">
+    <row r="107" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="2"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
@@ -4685,7 +4986,7 @@
       <c r="Y107" s="3"/>
       <c r="Z107" s="3"/>
     </row>
-    <row r="108" ht="15.75" customHeight="1">
+    <row r="108" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="2"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
@@ -4713,7 +5014,7 @@
       <c r="Y108" s="3"/>
       <c r="Z108" s="3"/>
     </row>
-    <row r="109" ht="15.75" customHeight="1">
+    <row r="109" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="2"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
@@ -4741,7 +5042,7 @@
       <c r="Y109" s="3"/>
       <c r="Z109" s="3"/>
     </row>
-    <row r="110" ht="15.75" customHeight="1">
+    <row r="110" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="2"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
@@ -4769,7 +5070,7 @@
       <c r="Y110" s="3"/>
       <c r="Z110" s="3"/>
     </row>
-    <row r="111" ht="15.75" customHeight="1">
+    <row r="111" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="2"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
@@ -4797,7 +5098,7 @@
       <c r="Y111" s="3"/>
       <c r="Z111" s="3"/>
     </row>
-    <row r="112" ht="15.75" customHeight="1">
+    <row r="112" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="2"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
@@ -4825,7 +5126,7 @@
       <c r="Y112" s="3"/>
       <c r="Z112" s="3"/>
     </row>
-    <row r="113" ht="15.75" customHeight="1">
+    <row r="113" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="2"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
@@ -4853,7 +5154,7 @@
       <c r="Y113" s="3"/>
       <c r="Z113" s="3"/>
     </row>
-    <row r="114" ht="15.75" customHeight="1">
+    <row r="114" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="2"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
@@ -4881,7 +5182,7 @@
       <c r="Y114" s="3"/>
       <c r="Z114" s="3"/>
     </row>
-    <row r="115" ht="15.75" customHeight="1">
+    <row r="115" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="2"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
@@ -4909,7 +5210,7 @@
       <c r="Y115" s="3"/>
       <c r="Z115" s="3"/>
     </row>
-    <row r="116" ht="15.75" customHeight="1">
+    <row r="116" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="2"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
@@ -4937,7 +5238,7 @@
       <c r="Y116" s="3"/>
       <c r="Z116" s="3"/>
     </row>
-    <row r="117" ht="15.75" customHeight="1">
+    <row r="117" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="2"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
@@ -4965,7 +5266,7 @@
       <c r="Y117" s="3"/>
       <c r="Z117" s="3"/>
     </row>
-    <row r="118" ht="15.75" customHeight="1">
+    <row r="118" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="2"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
@@ -4993,7 +5294,7 @@
       <c r="Y118" s="3"/>
       <c r="Z118" s="3"/>
     </row>
-    <row r="119" ht="15.75" customHeight="1">
+    <row r="119" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="2"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
@@ -5021,7 +5322,7 @@
       <c r="Y119" s="3"/>
       <c r="Z119" s="3"/>
     </row>
-    <row r="120" ht="15.75" customHeight="1">
+    <row r="120" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="2"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
@@ -5049,7 +5350,7 @@
       <c r="Y120" s="3"/>
       <c r="Z120" s="3"/>
     </row>
-    <row r="121" ht="15.75" customHeight="1">
+    <row r="121" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="2"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
@@ -5077,7 +5378,7 @@
       <c r="Y121" s="3"/>
       <c r="Z121" s="3"/>
     </row>
-    <row r="122" ht="15.75" customHeight="1">
+    <row r="122" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="2"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
@@ -5105,7 +5406,7 @@
       <c r="Y122" s="3"/>
       <c r="Z122" s="3"/>
     </row>
-    <row r="123" ht="15.75" customHeight="1">
+    <row r="123" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="2"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
@@ -5133,7 +5434,7 @@
       <c r="Y123" s="3"/>
       <c r="Z123" s="3"/>
     </row>
-    <row r="124" ht="15.75" customHeight="1">
+    <row r="124" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="2"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
@@ -5161,7 +5462,7 @@
       <c r="Y124" s="3"/>
       <c r="Z124" s="3"/>
     </row>
-    <row r="125" ht="15.75" customHeight="1">
+    <row r="125" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="2"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
@@ -5189,7 +5490,7 @@
       <c r="Y125" s="3"/>
       <c r="Z125" s="3"/>
     </row>
-    <row r="126" ht="15.75" customHeight="1">
+    <row r="126" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="2"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
@@ -5217,7 +5518,7 @@
       <c r="Y126" s="3"/>
       <c r="Z126" s="3"/>
     </row>
-    <row r="127" ht="15.75" customHeight="1">
+    <row r="127" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="2"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
@@ -5245,7 +5546,7 @@
       <c r="Y127" s="3"/>
       <c r="Z127" s="3"/>
     </row>
-    <row r="128" ht="15.75" customHeight="1">
+    <row r="128" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="2"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
@@ -5273,7 +5574,7 @@
       <c r="Y128" s="3"/>
       <c r="Z128" s="3"/>
     </row>
-    <row r="129" ht="15.75" customHeight="1">
+    <row r="129" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="2"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
@@ -5301,7 +5602,7 @@
       <c r="Y129" s="3"/>
       <c r="Z129" s="3"/>
     </row>
-    <row r="130" ht="15.75" customHeight="1">
+    <row r="130" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="2"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
@@ -5329,7 +5630,7 @@
       <c r="Y130" s="3"/>
       <c r="Z130" s="3"/>
     </row>
-    <row r="131" ht="15.75" customHeight="1">
+    <row r="131" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="2"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
@@ -5357,7 +5658,7 @@
       <c r="Y131" s="3"/>
       <c r="Z131" s="3"/>
     </row>
-    <row r="132" ht="15.75" customHeight="1">
+    <row r="132" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="2"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
@@ -5385,7 +5686,7 @@
       <c r="Y132" s="3"/>
       <c r="Z132" s="3"/>
     </row>
-    <row r="133" ht="15.75" customHeight="1">
+    <row r="133" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="2"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
@@ -5413,7 +5714,7 @@
       <c r="Y133" s="3"/>
       <c r="Z133" s="3"/>
     </row>
-    <row r="134" ht="15.75" customHeight="1">
+    <row r="134" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="2"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
@@ -5441,7 +5742,7 @@
       <c r="Y134" s="3"/>
       <c r="Z134" s="3"/>
     </row>
-    <row r="135" ht="15.75" customHeight="1">
+    <row r="135" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="2"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
@@ -5469,7 +5770,7 @@
       <c r="Y135" s="3"/>
       <c r="Z135" s="3"/>
     </row>
-    <row r="136" ht="15.75" customHeight="1">
+    <row r="136" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="2"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
@@ -5497,7 +5798,7 @@
       <c r="Y136" s="3"/>
       <c r="Z136" s="3"/>
     </row>
-    <row r="137" ht="15.75" customHeight="1">
+    <row r="137" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="2"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
@@ -5525,7 +5826,7 @@
       <c r="Y137" s="3"/>
       <c r="Z137" s="3"/>
     </row>
-    <row r="138" ht="15.75" customHeight="1">
+    <row r="138" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="2"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
@@ -5553,7 +5854,7 @@
       <c r="Y138" s="3"/>
       <c r="Z138" s="3"/>
     </row>
-    <row r="139" ht="15.75" customHeight="1">
+    <row r="139" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="2"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
@@ -5581,7 +5882,7 @@
       <c r="Y139" s="3"/>
       <c r="Z139" s="3"/>
     </row>
-    <row r="140" ht="15.75" customHeight="1">
+    <row r="140" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="2"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
@@ -5609,7 +5910,7 @@
       <c r="Y140" s="3"/>
       <c r="Z140" s="3"/>
     </row>
-    <row r="141" ht="15.75" customHeight="1">
+    <row r="141" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="2"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
@@ -5637,7 +5938,7 @@
       <c r="Y141" s="3"/>
       <c r="Z141" s="3"/>
     </row>
-    <row r="142" ht="15.75" customHeight="1">
+    <row r="142" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="2"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
@@ -5665,7 +5966,7 @@
       <c r="Y142" s="3"/>
       <c r="Z142" s="3"/>
     </row>
-    <row r="143" ht="15.75" customHeight="1">
+    <row r="143" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="2"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
@@ -5693,7 +5994,7 @@
       <c r="Y143" s="3"/>
       <c r="Z143" s="3"/>
     </row>
-    <row r="144" ht="15.75" customHeight="1">
+    <row r="144" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="2"/>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
@@ -5721,7 +6022,7 @@
       <c r="Y144" s="3"/>
       <c r="Z144" s="3"/>
     </row>
-    <row r="145" ht="15.75" customHeight="1">
+    <row r="145" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="2"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
@@ -5749,7 +6050,7 @@
       <c r="Y145" s="3"/>
       <c r="Z145" s="3"/>
     </row>
-    <row r="146" ht="15.75" customHeight="1">
+    <row r="146" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="2"/>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
@@ -5777,7 +6078,7 @@
       <c r="Y146" s="3"/>
       <c r="Z146" s="3"/>
     </row>
-    <row r="147" ht="15.75" customHeight="1">
+    <row r="147" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="2"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
@@ -5805,7 +6106,7 @@
       <c r="Y147" s="3"/>
       <c r="Z147" s="3"/>
     </row>
-    <row r="148" ht="15.75" customHeight="1">
+    <row r="148" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="2"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
@@ -5833,7 +6134,7 @@
       <c r="Y148" s="3"/>
       <c r="Z148" s="3"/>
     </row>
-    <row r="149" ht="15.75" customHeight="1">
+    <row r="149" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="2"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
@@ -5861,7 +6162,7 @@
       <c r="Y149" s="3"/>
       <c r="Z149" s="3"/>
     </row>
-    <row r="150" ht="15.75" customHeight="1">
+    <row r="150" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="2"/>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
@@ -5889,7 +6190,7 @@
       <c r="Y150" s="3"/>
       <c r="Z150" s="3"/>
     </row>
-    <row r="151" ht="15.75" customHeight="1">
+    <row r="151" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="2"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
@@ -5917,7 +6218,7 @@
       <c r="Y151" s="3"/>
       <c r="Z151" s="3"/>
     </row>
-    <row r="152" ht="15.75" customHeight="1">
+    <row r="152" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="2"/>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
@@ -5945,7 +6246,7 @@
       <c r="Y152" s="3"/>
       <c r="Z152" s="3"/>
     </row>
-    <row r="153" ht="15.75" customHeight="1">
+    <row r="153" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="2"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
@@ -5973,7 +6274,7 @@
       <c r="Y153" s="3"/>
       <c r="Z153" s="3"/>
     </row>
-    <row r="154" ht="15.75" customHeight="1">
+    <row r="154" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="2"/>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
@@ -6001,7 +6302,7 @@
       <c r="Y154" s="3"/>
       <c r="Z154" s="3"/>
     </row>
-    <row r="155" ht="15.75" customHeight="1">
+    <row r="155" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="2"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
@@ -6029,7 +6330,7 @@
       <c r="Y155" s="3"/>
       <c r="Z155" s="3"/>
     </row>
-    <row r="156" ht="15.75" customHeight="1">
+    <row r="156" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="2"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
@@ -6057,7 +6358,7 @@
       <c r="Y156" s="3"/>
       <c r="Z156" s="3"/>
     </row>
-    <row r="157" ht="15.75" customHeight="1">
+    <row r="157" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="2"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
@@ -6085,7 +6386,7 @@
       <c r="Y157" s="3"/>
       <c r="Z157" s="3"/>
     </row>
-    <row r="158" ht="15.75" customHeight="1">
+    <row r="158" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="2"/>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
@@ -6113,7 +6414,7 @@
       <c r="Y158" s="3"/>
       <c r="Z158" s="3"/>
     </row>
-    <row r="159" ht="15.75" customHeight="1">
+    <row r="159" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="2"/>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
@@ -6141,7 +6442,7 @@
       <c r="Y159" s="3"/>
       <c r="Z159" s="3"/>
     </row>
-    <row r="160" ht="15.75" customHeight="1">
+    <row r="160" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="2"/>
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
@@ -6169,7 +6470,7 @@
       <c r="Y160" s="3"/>
       <c r="Z160" s="3"/>
     </row>
-    <row r="161" ht="15.75" customHeight="1">
+    <row r="161" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="2"/>
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
@@ -6197,7 +6498,7 @@
       <c r="Y161" s="3"/>
       <c r="Z161" s="3"/>
     </row>
-    <row r="162" ht="15.75" customHeight="1">
+    <row r="162" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="2"/>
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
@@ -6225,7 +6526,7 @@
       <c r="Y162" s="3"/>
       <c r="Z162" s="3"/>
     </row>
-    <row r="163" ht="15.75" customHeight="1">
+    <row r="163" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="2"/>
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
@@ -6253,7 +6554,7 @@
       <c r="Y163" s="3"/>
       <c r="Z163" s="3"/>
     </row>
-    <row r="164" ht="15.75" customHeight="1">
+    <row r="164" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="2"/>
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
@@ -6281,7 +6582,7 @@
       <c r="Y164" s="3"/>
       <c r="Z164" s="3"/>
     </row>
-    <row r="165" ht="15.75" customHeight="1">
+    <row r="165" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="2"/>
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
@@ -6309,7 +6610,7 @@
       <c r="Y165" s="3"/>
       <c r="Z165" s="3"/>
     </row>
-    <row r="166" ht="15.75" customHeight="1">
+    <row r="166" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="2"/>
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
@@ -6337,7 +6638,7 @@
       <c r="Y166" s="3"/>
       <c r="Z166" s="3"/>
     </row>
-    <row r="167" ht="15.75" customHeight="1">
+    <row r="167" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="2"/>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
@@ -6365,7 +6666,7 @@
       <c r="Y167" s="3"/>
       <c r="Z167" s="3"/>
     </row>
-    <row r="168" ht="15.75" customHeight="1">
+    <row r="168" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="2"/>
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
@@ -6393,7 +6694,7 @@
       <c r="Y168" s="3"/>
       <c r="Z168" s="3"/>
     </row>
-    <row r="169" ht="15.75" customHeight="1">
+    <row r="169" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="2"/>
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
@@ -6421,7 +6722,7 @@
       <c r="Y169" s="3"/>
       <c r="Z169" s="3"/>
     </row>
-    <row r="170" ht="15.75" customHeight="1">
+    <row r="170" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="2"/>
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
@@ -6449,7 +6750,7 @@
       <c r="Y170" s="3"/>
       <c r="Z170" s="3"/>
     </row>
-    <row r="171" ht="15.75" customHeight="1">
+    <row r="171" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="2"/>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
@@ -6477,7 +6778,7 @@
       <c r="Y171" s="3"/>
       <c r="Z171" s="3"/>
     </row>
-    <row r="172" ht="15.75" customHeight="1">
+    <row r="172" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="2"/>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
@@ -6505,7 +6806,7 @@
       <c r="Y172" s="3"/>
       <c r="Z172" s="3"/>
     </row>
-    <row r="173" ht="15.75" customHeight="1">
+    <row r="173" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="2"/>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
@@ -6533,7 +6834,7 @@
       <c r="Y173" s="3"/>
       <c r="Z173" s="3"/>
     </row>
-    <row r="174" ht="15.75" customHeight="1">
+    <row r="174" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="2"/>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
@@ -6561,7 +6862,7 @@
       <c r="Y174" s="3"/>
       <c r="Z174" s="3"/>
     </row>
-    <row r="175" ht="15.75" customHeight="1">
+    <row r="175" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="2"/>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
@@ -6589,7 +6890,7 @@
       <c r="Y175" s="3"/>
       <c r="Z175" s="3"/>
     </row>
-    <row r="176" ht="15.75" customHeight="1">
+    <row r="176" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="2"/>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
@@ -6617,7 +6918,7 @@
       <c r="Y176" s="3"/>
       <c r="Z176" s="3"/>
     </row>
-    <row r="177" ht="15.75" customHeight="1">
+    <row r="177" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="2"/>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
@@ -6645,7 +6946,7 @@
       <c r="Y177" s="3"/>
       <c r="Z177" s="3"/>
     </row>
-    <row r="178" ht="15.75" customHeight="1">
+    <row r="178" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="2"/>
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
@@ -6673,7 +6974,7 @@
       <c r="Y178" s="3"/>
       <c r="Z178" s="3"/>
     </row>
-    <row r="179" ht="15.75" customHeight="1">
+    <row r="179" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="2"/>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
@@ -6701,7 +7002,7 @@
       <c r="Y179" s="3"/>
       <c r="Z179" s="3"/>
     </row>
-    <row r="180" ht="15.75" customHeight="1">
+    <row r="180" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="2"/>
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
@@ -6729,7 +7030,7 @@
       <c r="Y180" s="3"/>
       <c r="Z180" s="3"/>
     </row>
-    <row r="181" ht="15.75" customHeight="1">
+    <row r="181" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="2"/>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
@@ -6757,7 +7058,7 @@
       <c r="Y181" s="3"/>
       <c r="Z181" s="3"/>
     </row>
-    <row r="182" ht="15.75" customHeight="1">
+    <row r="182" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="2"/>
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
@@ -6785,7 +7086,7 @@
       <c r="Y182" s="3"/>
       <c r="Z182" s="3"/>
     </row>
-    <row r="183" ht="15.75" customHeight="1">
+    <row r="183" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="2"/>
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
@@ -6813,7 +7114,7 @@
       <c r="Y183" s="3"/>
       <c r="Z183" s="3"/>
     </row>
-    <row r="184" ht="15.75" customHeight="1">
+    <row r="184" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="2"/>
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
@@ -6841,7 +7142,7 @@
       <c r="Y184" s="3"/>
       <c r="Z184" s="3"/>
     </row>
-    <row r="185" ht="15.75" customHeight="1">
+    <row r="185" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="2"/>
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
@@ -6869,7 +7170,7 @@
       <c r="Y185" s="3"/>
       <c r="Z185" s="3"/>
     </row>
-    <row r="186" ht="15.75" customHeight="1">
+    <row r="186" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="2"/>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
@@ -6897,7 +7198,7 @@
       <c r="Y186" s="3"/>
       <c r="Z186" s="3"/>
     </row>
-    <row r="187" ht="15.75" customHeight="1">
+    <row r="187" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="2"/>
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
@@ -6925,7 +7226,7 @@
       <c r="Y187" s="3"/>
       <c r="Z187" s="3"/>
     </row>
-    <row r="188" ht="15.75" customHeight="1">
+    <row r="188" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="2"/>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
@@ -6953,7 +7254,7 @@
       <c r="Y188" s="3"/>
       <c r="Z188" s="3"/>
     </row>
-    <row r="189" ht="15.75" customHeight="1">
+    <row r="189" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="2"/>
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
@@ -6981,7 +7282,7 @@
       <c r="Y189" s="3"/>
       <c r="Z189" s="3"/>
     </row>
-    <row r="190" ht="15.75" customHeight="1">
+    <row r="190" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="2"/>
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
@@ -7009,7 +7310,7 @@
       <c r="Y190" s="3"/>
       <c r="Z190" s="3"/>
     </row>
-    <row r="191" ht="15.75" customHeight="1">
+    <row r="191" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="2"/>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
@@ -7037,7 +7338,7 @@
       <c r="Y191" s="3"/>
       <c r="Z191" s="3"/>
     </row>
-    <row r="192" ht="15.75" customHeight="1">
+    <row r="192" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="2"/>
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
@@ -7065,7 +7366,7 @@
       <c r="Y192" s="3"/>
       <c r="Z192" s="3"/>
     </row>
-    <row r="193" ht="15.75" customHeight="1">
+    <row r="193" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="2"/>
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
@@ -7093,7 +7394,7 @@
       <c r="Y193" s="3"/>
       <c r="Z193" s="3"/>
     </row>
-    <row r="194" ht="15.75" customHeight="1">
+    <row r="194" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="2"/>
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
@@ -7121,7 +7422,7 @@
       <c r="Y194" s="3"/>
       <c r="Z194" s="3"/>
     </row>
-    <row r="195" ht="15.75" customHeight="1">
+    <row r="195" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="2"/>
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
@@ -7149,7 +7450,7 @@
       <c r="Y195" s="3"/>
       <c r="Z195" s="3"/>
     </row>
-    <row r="196" ht="15.75" customHeight="1">
+    <row r="196" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="2"/>
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
@@ -7177,7 +7478,7 @@
       <c r="Y196" s="3"/>
       <c r="Z196" s="3"/>
     </row>
-    <row r="197" ht="15.75" customHeight="1">
+    <row r="197" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="2"/>
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
@@ -7205,7 +7506,7 @@
       <c r="Y197" s="3"/>
       <c r="Z197" s="3"/>
     </row>
-    <row r="198" ht="15.75" customHeight="1">
+    <row r="198" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="2"/>
       <c r="B198" s="3"/>
       <c r="C198" s="3"/>
@@ -7233,7 +7534,7 @@
       <c r="Y198" s="3"/>
       <c r="Z198" s="3"/>
     </row>
-    <row r="199" ht="15.75" customHeight="1">
+    <row r="199" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="2"/>
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
@@ -7261,7 +7562,7 @@
       <c r="Y199" s="3"/>
       <c r="Z199" s="3"/>
     </row>
-    <row r="200" ht="15.75" customHeight="1">
+    <row r="200" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="2"/>
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
@@ -7289,7 +7590,7 @@
       <c r="Y200" s="3"/>
       <c r="Z200" s="3"/>
     </row>
-    <row r="201" ht="15.75" customHeight="1">
+    <row r="201" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="2"/>
       <c r="B201" s="3"/>
       <c r="C201" s="3"/>
@@ -7317,7 +7618,7 @@
       <c r="Y201" s="3"/>
       <c r="Z201" s="3"/>
     </row>
-    <row r="202" ht="15.75" customHeight="1">
+    <row r="202" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="2"/>
       <c r="B202" s="3"/>
       <c r="C202" s="3"/>
@@ -7345,7 +7646,7 @@
       <c r="Y202" s="3"/>
       <c r="Z202" s="3"/>
     </row>
-    <row r="203" ht="15.75" customHeight="1">
+    <row r="203" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="2"/>
       <c r="B203" s="3"/>
       <c r="C203" s="3"/>
@@ -7373,7 +7674,7 @@
       <c r="Y203" s="3"/>
       <c r="Z203" s="3"/>
     </row>
-    <row r="204" ht="15.75" customHeight="1">
+    <row r="204" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="2"/>
       <c r="B204" s="3"/>
       <c r="C204" s="3"/>
@@ -7401,7 +7702,7 @@
       <c r="Y204" s="3"/>
       <c r="Z204" s="3"/>
     </row>
-    <row r="205" ht="15.75" customHeight="1">
+    <row r="205" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="2"/>
       <c r="B205" s="3"/>
       <c r="C205" s="3"/>
@@ -7429,7 +7730,7 @@
       <c r="Y205" s="3"/>
       <c r="Z205" s="3"/>
     </row>
-    <row r="206" ht="15.75" customHeight="1">
+    <row r="206" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="2"/>
       <c r="B206" s="3"/>
       <c r="C206" s="3"/>
@@ -7457,7 +7758,7 @@
       <c r="Y206" s="3"/>
       <c r="Z206" s="3"/>
     </row>
-    <row r="207" ht="15.75" customHeight="1">
+    <row r="207" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="2"/>
       <c r="B207" s="3"/>
       <c r="C207" s="3"/>
@@ -7485,7 +7786,7 @@
       <c r="Y207" s="3"/>
       <c r="Z207" s="3"/>
     </row>
-    <row r="208" ht="15.75" customHeight="1">
+    <row r="208" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="2"/>
       <c r="B208" s="3"/>
       <c r="C208" s="3"/>
@@ -7513,7 +7814,7 @@
       <c r="Y208" s="3"/>
       <c r="Z208" s="3"/>
     </row>
-    <row r="209" ht="15.75" customHeight="1">
+    <row r="209" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="2"/>
       <c r="B209" s="3"/>
       <c r="C209" s="3"/>
@@ -7541,7 +7842,7 @@
       <c r="Y209" s="3"/>
       <c r="Z209" s="3"/>
     </row>
-    <row r="210" ht="15.75" customHeight="1">
+    <row r="210" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="2"/>
       <c r="B210" s="3"/>
       <c r="C210" s="3"/>
@@ -7569,7 +7870,7 @@
       <c r="Y210" s="3"/>
       <c r="Z210" s="3"/>
     </row>
-    <row r="211" ht="15.75" customHeight="1">
+    <row r="211" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="2"/>
       <c r="B211" s="3"/>
       <c r="C211" s="3"/>
@@ -7597,7 +7898,7 @@
       <c r="Y211" s="3"/>
       <c r="Z211" s="3"/>
     </row>
-    <row r="212" ht="15.75" customHeight="1">
+    <row r="212" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="2"/>
       <c r="B212" s="3"/>
       <c r="C212" s="3"/>
@@ -7625,7 +7926,7 @@
       <c r="Y212" s="3"/>
       <c r="Z212" s="3"/>
     </row>
-    <row r="213" ht="15.75" customHeight="1">
+    <row r="213" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="2"/>
       <c r="B213" s="3"/>
       <c r="C213" s="3"/>
@@ -7653,7 +7954,7 @@
       <c r="Y213" s="3"/>
       <c r="Z213" s="3"/>
     </row>
-    <row r="214" ht="15.75" customHeight="1">
+    <row r="214" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="2"/>
       <c r="B214" s="3"/>
       <c r="C214" s="3"/>
@@ -7681,7 +7982,7 @@
       <c r="Y214" s="3"/>
       <c r="Z214" s="3"/>
     </row>
-    <row r="215" ht="15.75" customHeight="1">
+    <row r="215" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="2"/>
       <c r="B215" s="3"/>
       <c r="C215" s="3"/>
@@ -7709,7 +8010,7 @@
       <c r="Y215" s="3"/>
       <c r="Z215" s="3"/>
     </row>
-    <row r="216" ht="15.75" customHeight="1">
+    <row r="216" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="2"/>
       <c r="B216" s="3"/>
       <c r="C216" s="3"/>
@@ -7737,7 +8038,7 @@
       <c r="Y216" s="3"/>
       <c r="Z216" s="3"/>
     </row>
-    <row r="217" ht="15.75" customHeight="1">
+    <row r="217" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="2"/>
       <c r="B217" s="3"/>
       <c r="C217" s="3"/>
@@ -7765,7 +8066,7 @@
       <c r="Y217" s="3"/>
       <c r="Z217" s="3"/>
     </row>
-    <row r="218" ht="15.75" customHeight="1">
+    <row r="218" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="2"/>
       <c r="B218" s="3"/>
       <c r="C218" s="3"/>
@@ -7793,7 +8094,7 @@
       <c r="Y218" s="3"/>
       <c r="Z218" s="3"/>
     </row>
-    <row r="219" ht="15.75" customHeight="1">
+    <row r="219" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="2"/>
       <c r="B219" s="3"/>
       <c r="C219" s="3"/>
@@ -7821,7 +8122,7 @@
       <c r="Y219" s="3"/>
       <c r="Z219" s="3"/>
     </row>
-    <row r="220" ht="15.75" customHeight="1">
+    <row r="220" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="2"/>
       <c r="B220" s="3"/>
       <c r="C220" s="3"/>
@@ -7849,7 +8150,7 @@
       <c r="Y220" s="3"/>
       <c r="Z220" s="3"/>
     </row>
-    <row r="221" ht="15.75" customHeight="1">
+    <row r="221" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="2"/>
       <c r="B221" s="3"/>
       <c r="C221" s="3"/>
@@ -7877,7 +8178,7 @@
       <c r="Y221" s="3"/>
       <c r="Z221" s="3"/>
     </row>
-    <row r="222" ht="15.75" customHeight="1">
+    <row r="222" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="2"/>
       <c r="B222" s="3"/>
       <c r="C222" s="3"/>
@@ -7905,7 +8206,7 @@
       <c r="Y222" s="3"/>
       <c r="Z222" s="3"/>
     </row>
-    <row r="223" ht="15.75" customHeight="1">
+    <row r="223" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="2"/>
       <c r="B223" s="3"/>
       <c r="C223" s="3"/>
@@ -7933,7 +8234,7 @@
       <c r="Y223" s="3"/>
       <c r="Z223" s="3"/>
     </row>
-    <row r="224" ht="15.75" customHeight="1">
+    <row r="224" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="2"/>
       <c r="B224" s="3"/>
       <c r="C224" s="3"/>
@@ -7961,7 +8262,7 @@
       <c r="Y224" s="3"/>
       <c r="Z224" s="3"/>
     </row>
-    <row r="225" ht="15.75" customHeight="1">
+    <row r="225" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="2"/>
       <c r="B225" s="3"/>
       <c r="C225" s="3"/>
@@ -7989,7 +8290,7 @@
       <c r="Y225" s="3"/>
       <c r="Z225" s="3"/>
     </row>
-    <row r="226" ht="15.75" customHeight="1">
+    <row r="226" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="2"/>
       <c r="B226" s="3"/>
       <c r="C226" s="3"/>
@@ -8017,7 +8318,7 @@
       <c r="Y226" s="3"/>
       <c r="Z226" s="3"/>
     </row>
-    <row r="227" ht="15.75" customHeight="1">
+    <row r="227" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="2"/>
       <c r="B227" s="3"/>
       <c r="C227" s="3"/>
@@ -8045,7 +8346,7 @@
       <c r="Y227" s="3"/>
       <c r="Z227" s="3"/>
     </row>
-    <row r="228" ht="15.75" customHeight="1">
+    <row r="228" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="2"/>
       <c r="B228" s="3"/>
       <c r="C228" s="3"/>
@@ -8073,7 +8374,7 @@
       <c r="Y228" s="3"/>
       <c r="Z228" s="3"/>
     </row>
-    <row r="229" ht="15.75" customHeight="1">
+    <row r="229" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="2"/>
       <c r="B229" s="3"/>
       <c r="C229" s="3"/>
@@ -8101,7 +8402,7 @@
       <c r="Y229" s="3"/>
       <c r="Z229" s="3"/>
     </row>
-    <row r="230" ht="15.75" customHeight="1">
+    <row r="230" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="2"/>
       <c r="B230" s="3"/>
       <c r="C230" s="3"/>
@@ -8129,7 +8430,7 @@
       <c r="Y230" s="3"/>
       <c r="Z230" s="3"/>
     </row>
-    <row r="231" ht="15.75" customHeight="1">
+    <row r="231" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="2"/>
       <c r="B231" s="3"/>
       <c r="C231" s="3"/>
@@ -8157,7 +8458,7 @@
       <c r="Y231" s="3"/>
       <c r="Z231" s="3"/>
     </row>
-    <row r="232" ht="15.75" customHeight="1">
+    <row r="232" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="2"/>
       <c r="B232" s="3"/>
       <c r="C232" s="3"/>
@@ -8185,7 +8486,7 @@
       <c r="Y232" s="3"/>
       <c r="Z232" s="3"/>
     </row>
-    <row r="233" ht="15.75" customHeight="1">
+    <row r="233" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="2"/>
       <c r="B233" s="3"/>
       <c r="C233" s="3"/>
@@ -8213,7 +8514,7 @@
       <c r="Y233" s="3"/>
       <c r="Z233" s="3"/>
     </row>
-    <row r="234" ht="15.75" customHeight="1">
+    <row r="234" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="2"/>
       <c r="B234" s="3"/>
       <c r="C234" s="3"/>
@@ -8241,7 +8542,7 @@
       <c r="Y234" s="3"/>
       <c r="Z234" s="3"/>
     </row>
-    <row r="235" ht="15.75" customHeight="1">
+    <row r="235" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="2"/>
       <c r="B235" s="3"/>
       <c r="C235" s="3"/>
@@ -8269,7 +8570,7 @@
       <c r="Y235" s="3"/>
       <c r="Z235" s="3"/>
     </row>
-    <row r="236" ht="15.75" customHeight="1">
+    <row r="236" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="2"/>
       <c r="B236" s="3"/>
       <c r="C236" s="3"/>
@@ -8297,7 +8598,7 @@
       <c r="Y236" s="3"/>
       <c r="Z236" s="3"/>
     </row>
-    <row r="237" ht="15.75" customHeight="1">
+    <row r="237" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="2"/>
       <c r="B237" s="3"/>
       <c r="C237" s="3"/>
@@ -8325,7 +8626,7 @@
       <c r="Y237" s="3"/>
       <c r="Z237" s="3"/>
     </row>
-    <row r="238" ht="15.75" customHeight="1">
+    <row r="238" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="2"/>
       <c r="B238" s="3"/>
       <c r="C238" s="3"/>
@@ -8353,7 +8654,7 @@
       <c r="Y238" s="3"/>
       <c r="Z238" s="3"/>
     </row>
-    <row r="239" ht="15.75" customHeight="1">
+    <row r="239" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="2"/>
       <c r="B239" s="3"/>
       <c r="C239" s="3"/>
@@ -8381,7 +8682,7 @@
       <c r="Y239" s="3"/>
       <c r="Z239" s="3"/>
     </row>
-    <row r="240" ht="15.75" customHeight="1">
+    <row r="240" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="2"/>
       <c r="B240" s="3"/>
       <c r="C240" s="3"/>
@@ -8409,7 +8710,7 @@
       <c r="Y240" s="3"/>
       <c r="Z240" s="3"/>
     </row>
-    <row r="241" ht="15.75" customHeight="1">
+    <row r="241" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="2"/>
       <c r="B241" s="3"/>
       <c r="C241" s="3"/>
@@ -8437,7 +8738,7 @@
       <c r="Y241" s="3"/>
       <c r="Z241" s="3"/>
     </row>
-    <row r="242" ht="15.75" customHeight="1">
+    <row r="242" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="2"/>
       <c r="B242" s="3"/>
       <c r="C242" s="3"/>
@@ -8465,7 +8766,7 @@
       <c r="Y242" s="3"/>
       <c r="Z242" s="3"/>
     </row>
-    <row r="243" ht="15.75" customHeight="1">
+    <row r="243" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="2"/>
       <c r="B243" s="3"/>
       <c r="C243" s="3"/>
@@ -8493,7 +8794,7 @@
       <c r="Y243" s="3"/>
       <c r="Z243" s="3"/>
     </row>
-    <row r="244" ht="15.75" customHeight="1">
+    <row r="244" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="2"/>
       <c r="B244" s="3"/>
       <c r="C244" s="3"/>
@@ -8521,7 +8822,7 @@
       <c r="Y244" s="3"/>
       <c r="Z244" s="3"/>
     </row>
-    <row r="245" ht="15.75" customHeight="1">
+    <row r="245" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="2"/>
       <c r="B245" s="3"/>
       <c r="C245" s="3"/>
@@ -8549,7 +8850,7 @@
       <c r="Y245" s="3"/>
       <c r="Z245" s="3"/>
     </row>
-    <row r="246" ht="15.75" customHeight="1">
+    <row r="246" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="2"/>
       <c r="B246" s="3"/>
       <c r="C246" s="3"/>
@@ -8577,7 +8878,7 @@
       <c r="Y246" s="3"/>
       <c r="Z246" s="3"/>
     </row>
-    <row r="247" ht="15.75" customHeight="1">
+    <row r="247" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="2"/>
       <c r="B247" s="3"/>
       <c r="C247" s="3"/>
@@ -8605,7 +8906,7 @@
       <c r="Y247" s="3"/>
       <c r="Z247" s="3"/>
     </row>
-    <row r="248" ht="15.75" customHeight="1">
+    <row r="248" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="2"/>
       <c r="B248" s="3"/>
       <c r="C248" s="3"/>
@@ -8633,7 +8934,7 @@
       <c r="Y248" s="3"/>
       <c r="Z248" s="3"/>
     </row>
-    <row r="249" ht="15.75" customHeight="1">
+    <row r="249" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="2"/>
       <c r="B249" s="3"/>
       <c r="C249" s="3"/>
@@ -8661,7 +8962,7 @@
       <c r="Y249" s="3"/>
       <c r="Z249" s="3"/>
     </row>
-    <row r="250" ht="15.75" customHeight="1">
+    <row r="250" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="2"/>
       <c r="B250" s="3"/>
       <c r="C250" s="3"/>
@@ -8689,7 +8990,7 @@
       <c r="Y250" s="3"/>
       <c r="Z250" s="3"/>
     </row>
-    <row r="251" ht="15.75" customHeight="1">
+    <row r="251" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="2"/>
       <c r="B251" s="3"/>
       <c r="C251" s="3"/>
@@ -8717,7 +9018,7 @@
       <c r="Y251" s="3"/>
       <c r="Z251" s="3"/>
     </row>
-    <row r="252" ht="15.75" customHeight="1">
+    <row r="252" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="2"/>
       <c r="B252" s="3"/>
       <c r="C252" s="3"/>
@@ -8745,7 +9046,7 @@
       <c r="Y252" s="3"/>
       <c r="Z252" s="3"/>
     </row>
-    <row r="253" ht="15.75" customHeight="1">
+    <row r="253" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="2"/>
       <c r="B253" s="3"/>
       <c r="C253" s="3"/>
@@ -8773,807 +9074,841 @@
       <c r="Y253" s="3"/>
       <c r="Z253" s="3"/>
     </row>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="254" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="177">
-    <mergeCell ref="J17:L17"/>
-    <mergeCell ref="M17:Q17"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="N14:O14"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="P15:Q15"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="N10:Q10"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="N8:Q8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="N9:Q9"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="N11:Q11"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="E11:G11"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="E10:G10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="J18:L18"/>
-    <mergeCell ref="M18:Q18"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="J29:L29"/>
-    <mergeCell ref="J30:L30"/>
-    <mergeCell ref="M30:Q30"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="B49:G49"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="J49:K49"/>
+    <mergeCell ref="L49:M49"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="L46:M46"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="J48:K48"/>
+    <mergeCell ref="L48:M48"/>
+    <mergeCell ref="N48:Q48"/>
+    <mergeCell ref="B46:G46"/>
+    <mergeCell ref="B47:G47"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="J47:K47"/>
+    <mergeCell ref="L47:M47"/>
+    <mergeCell ref="N47:Q47"/>
+    <mergeCell ref="B48:G48"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="N41:O41"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="J42:K42"/>
+    <mergeCell ref="N42:O42"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="N43:O43"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="J46:K46"/>
+    <mergeCell ref="N46:Q46"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="L53:M53"/>
+    <mergeCell ref="L50:M50"/>
+    <mergeCell ref="N50:O50"/>
+    <mergeCell ref="L51:M51"/>
+    <mergeCell ref="N51:O51"/>
+    <mergeCell ref="P51:Q51"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="P52:Q52"/>
+    <mergeCell ref="N49:Q49"/>
+    <mergeCell ref="P50:Q50"/>
+    <mergeCell ref="N37:Q37"/>
+    <mergeCell ref="N38:Q38"/>
+    <mergeCell ref="J40:M40"/>
+    <mergeCell ref="N40:Q40"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="F39:I39"/>
+    <mergeCell ref="J39:M39"/>
+    <mergeCell ref="N39:Q39"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="F40:I40"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="F38:I38"/>
+    <mergeCell ref="J38:M38"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="J37:M37"/>
+    <mergeCell ref="J28:L28"/>
+    <mergeCell ref="M28:Q28"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="M29:Q29"/>
+    <mergeCell ref="N32:O32"/>
+    <mergeCell ref="N33:O33"/>
+    <mergeCell ref="N34:O34"/>
+    <mergeCell ref="N35:O35"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="E35:F35"/>
     <mergeCell ref="M31:Q31"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="B30:D30"/>
@@ -9598,6 +9933,15 @@
     <mergeCell ref="J21:K21"/>
     <mergeCell ref="N21:O21"/>
     <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="J18:L18"/>
+    <mergeCell ref="M18:Q18"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="J29:L29"/>
+    <mergeCell ref="J30:L30"/>
+    <mergeCell ref="M30:Q30"/>
     <mergeCell ref="N22:O22"/>
     <mergeCell ref="P22:Q22"/>
     <mergeCell ref="F23:G23"/>
@@ -9613,94 +9957,51 @@
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="E28:G28"/>
     <mergeCell ref="H28:I28"/>
-    <mergeCell ref="J28:L28"/>
-    <mergeCell ref="M28:Q28"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="M29:Q29"/>
-    <mergeCell ref="N32:O32"/>
-    <mergeCell ref="N33:O33"/>
-    <mergeCell ref="N34:O34"/>
-    <mergeCell ref="N35:O35"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="F38:I38"/>
-    <mergeCell ref="J38:M38"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="F37:I37"/>
-    <mergeCell ref="J37:M37"/>
-    <mergeCell ref="N37:Q37"/>
-    <mergeCell ref="N38:Q38"/>
-    <mergeCell ref="J40:M40"/>
-    <mergeCell ref="N40:Q40"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="F39:I39"/>
-    <mergeCell ref="J39:M39"/>
-    <mergeCell ref="N39:Q39"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="F40:I40"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="J46:K46"/>
-    <mergeCell ref="N46:Q46"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="L53:M53"/>
-    <mergeCell ref="L50:M50"/>
-    <mergeCell ref="N50:O50"/>
-    <mergeCell ref="L51:M51"/>
-    <mergeCell ref="N51:O51"/>
-    <mergeCell ref="P51:Q51"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="P52:Q52"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="N41:O41"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="J42:K42"/>
-    <mergeCell ref="N42:O42"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="J43:K43"/>
-    <mergeCell ref="N43:O43"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="L46:M46"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="J48:K48"/>
-    <mergeCell ref="L48:M48"/>
-    <mergeCell ref="N48:Q48"/>
-    <mergeCell ref="B46:G46"/>
-    <mergeCell ref="B47:G47"/>
-    <mergeCell ref="H47:I47"/>
-    <mergeCell ref="J47:K47"/>
-    <mergeCell ref="L47:M47"/>
-    <mergeCell ref="N47:Q47"/>
-    <mergeCell ref="B48:G48"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="B49:G49"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="J49:K49"/>
-    <mergeCell ref="L49:M49"/>
-    <mergeCell ref="N49:Q49"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="P50:Q50"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="N11:Q11"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="N10:Q10"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="N8:Q8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="N9:Q9"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="J17:L17"/>
+    <mergeCell ref="M17:Q17"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="N14:O14"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="H17:I17"/>
   </mergeCells>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>